--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.142.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.142.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.142" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.142" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.142.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.142.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0142.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0142.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -855,7 +855,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.142.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.142.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.142" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.142" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€ ï¼Œ co-</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00, U+FF0C FULLWIDTH COMMA :: 一 ， co-</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: \â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]135</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]135</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L33: isolated marker/symbol line :: 2</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: %</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]135</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -626,7 +630,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L82: line starts with punctuation glued to text :: _________years, under and by virtue of an indenture</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • was to be</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” years (or from year to year, or at, will) of</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: ； and C.' D., the defendant hereinafter named,</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: be dissolved from the -------day of â€¢ TÂ°</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: \•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,19 +685,19 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: /</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: \•</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: be dissolved from the -------day of â€¢ TÂ°</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: be dissolved from the -------day of • T°</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L93: line starts with punctuation glued to text :: * that your</t>
+          <t>L82: line starts with punctuation glued to text :: _________years, under and by virtue of an indenture</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -732,7 +736,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ was to be</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: be dissolved from the -------day of • T°</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -742,15 +746,23 @@
           <t>L94: isolated marker/symbol line :: 135</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L71: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L51: punctuation artifact: double/multiple hyphen :: of Â£-------</t>
+          <t>L51: punctuation artifact: double/multiple hyphen :: of £-------</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L93: line starts with punctuation glued to text :: * that your</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -771,7 +783,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -783,7 +795,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: _â€” years (or from year to year, or at will) of</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • was to be</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -793,7 +805,11 @@
           <t>L95: isolated marker/symbol line :: X</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L112: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
@@ -834,7 +850,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: reement un-â€¢</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: reement un-•</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -842,7 +858,11 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr"/>
       <c r="P6" s="1" t="inlineStr"/>
-      <c r="Q6" s="1" t="inlineStr"/>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: reement un-•</t>
+        </is>
+      </c>
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
@@ -875,11 +895,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 the said â€”â€”</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -986,7 +1002,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1025,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1064,7 +1080,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1103,7 +1119,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1142,7 +1158,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
